--- a/reports/scan/slack_cbg.xlsx
+++ b/reports/scan/slack_cbg.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
         <fgColor rgb="00FFCC99"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -72,13 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +521,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -569,7 +563,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -663,7 +657,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -703,9 +697,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -757,7 +751,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -804,7 +798,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -851,12 +845,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -891,14 +885,14 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -950,7 +944,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">

--- a/reports/scan/slack_cbg.xlsx
+++ b/reports/scan/slack_cbg.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -697,9 +697,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -744,9 +744,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -932,9 +932,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">

--- a/reports/scan/slack_cbg.xlsx
+++ b/reports/scan/slack_cbg.xlsx
@@ -697,9 +697,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -744,9 +744,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -932,9 +932,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
